--- a/output/pdf_financials_xlsx/KAPA.xlsx
+++ b/output/pdf_financials_xlsx/KAPA.xlsx
@@ -898,7 +898,7 @@
         <v>-0.03703</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.123855</v>
+        <v>-0.123855</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-2.699369</v>
@@ -1054,7 +1054,7 @@
         <v>-0.03703</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.123855</v>
+        <v>-0.123855</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-2.699369</v>
@@ -1147,7 +1147,7 @@
         <v>-0.03703</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.123855</v>
+        <v>-0.123855</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-2.699369</v>
@@ -1287,7 +1287,7 @@
         <v>-0.03703</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.123855</v>
+        <v>-0.123855</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.699369</v>
@@ -1349,7 +1349,7 @@
         <v>-0.03703</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.123855</v>
+        <v>-0.123855</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.699369</v>
@@ -1427,7 +1427,7 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -3378,25 +3378,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.055347</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.055347</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.02987</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.475088</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.573305</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.573305</v>
       </c>
     </row>
     <row r="93">
@@ -5368,7 +5368,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -7040,7 +7044,11 @@
           <t>Share-based payment reserve 4</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -7092,7 +7100,11 @@
           <t>Warrant reserve 4</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -7644,7 +7656,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -7698,7 +7714,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -14157,7 +14177,7 @@
         </is>
       </c>
       <c r="H169" s="5" t="n">
-        <v>0.123855</v>
+        <v>-0.123855</v>
       </c>
       <c r="I169" s="5" t="n">
         <v>-2.699369</v>

--- a/output/pdf_financials_xlsx/KAPA.xlsx
+++ b/output/pdf_financials_xlsx/KAPA.xlsx
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.004312</v>
       </c>
     </row>
     <row r="13">
@@ -1299,7 +1299,7 @@
         <v>-0.617501</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.484904</v>
+        <v>-0.489216</v>
       </c>
     </row>
     <row r="28">
@@ -1361,7 +1361,7 @@
         <v>-0.617501</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.484904</v>
+        <v>-0.489216</v>
       </c>
     </row>
     <row r="30">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.173267</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.268051</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.235681</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009332999999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.548615</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.527451</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.870545</v>
@@ -1565,22 +1565,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.173267</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.268051</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.235681</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009332999999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.548615</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.527451</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.870545</v>
@@ -1946,13 +1946,13 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.514377</v>
+        <v>1.505044</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.581028</v>
+        <v>0.032413</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.557044</v>
+        <v>0.029593</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.083908</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">

--- a/output/pdf_financials_xlsx/KAPA.xlsx
+++ b/output/pdf_financials_xlsx/KAPA.xlsx
@@ -617,13 +617,13 @@
         <v>0.011488</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.028</v>
+        <v>0.030727</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.417927</v>
+        <v>0.440576</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.456457</v>
+        <v>0.516285</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.359606</v>
@@ -2470,19 +2470,19 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.203018</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.159057</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.216243</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.218067</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.209665</v>
       </c>
     </row>
     <row r="65">
@@ -2563,19 +2563,19 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.047991</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.032709</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.041113</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.028498</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="68">
@@ -3577,13 +3577,13 @@
         <v>-0.03703</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.082964</v>
+        <v>-0.123855</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-2.699369</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-2.699369</v>
+        <v>-0.770932</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>-0.617501</v>
@@ -3639,19 +3639,19 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004084</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.002225</v>
+        <v>-0.002201</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.016118</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012228</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.011333</v>
       </c>
     </row>
     <row r="102">
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.006348</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>-0.032006</v>
@@ -3732,7 +3732,7 @@
         <v>0.00466</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.00494</v>
+        <v>0.07735300000000001</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>-0.116567</v>
@@ -3794,19 +3794,19 @@
         <v>0.00466</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.00494</v>
+        <v>0.07961699999999999</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.150798</v>
+        <v>-0.150774</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.08698699999999999</v>
+        <v>0.103105</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.061423</v>
+        <v>-0.07365099999999999</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.00233</v>
+        <v>-0.009003000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -3952,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0145</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0</v>
+        <v>-0.148456</v>
       </c>
       <c r="F119" s="3" t="n">
         <v>-0.228476</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>0.994115</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -4357,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.176456</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.176456</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.011327</v>
+        <v>1.452752</v>
       </c>
       <c r="F129" s="3" t="n">
         <v>1.259515</v>
@@ -4558,7 +4558,7 @@
         <v>0.268051</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0.235681</v>
+        <v>0.146807</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>1.365513</v>
@@ -4651,7 +4651,7 @@
         <v>0.235681</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0.168984</v>
+        <v>1.365513</v>
       </c>
       <c r="F133" s="3" t="n">
         <v>1.548615</v>
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0145</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>-0.03237</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.078024</v>
+        <v>-0.08559</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.8479370000000001</v>
+        <v>-0.862437</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.639923</v>
@@ -4739,7 +4739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L223"/>
+  <dimension ref="A1:L252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8274,7 +8274,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -8354,10 +8358,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J65" s="5" t="n">
+        <v>0.005014</v>
       </c>
       <c r="K65" s="5" t="n">
         <v>-0.054315</v>
@@ -8502,10 +8504,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H68" s="5" t="n">
+        <v>-0.148456</v>
       </c>
       <c r="I68" s="5" t="n">
         <v>-0.204705</v>
@@ -8610,10 +8610,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H70" s="5" t="n">
+        <v>-0.148456</v>
       </c>
       <c r="I70" s="5" t="n">
         <v>-0.228476</v>
@@ -8780,10 +8778,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>1.452752</v>
       </c>
       <c r="I73" s="5" t="n">
         <v>1.259515</v>
@@ -9493,7 +9489,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
+          <t>Loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9521,16 +9517,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n">
-        <v>-2.699369</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="5" t="n">
         <v>-0.770932</v>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K86" s="5" t="n">
+        <v>-0.617501</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -9546,15 +9542,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Proceeds from issuance of common shares, net of issuance costs.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -9575,18 +9575,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n">
-        <v>0.00565</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K87" s="5" t="n">
+        <v>0.994115</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -9602,29 +9602,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Listing expense</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.173267</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.09478399999999999</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.03237</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -9632,17 +9630,13 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>1.592538</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.183102</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>-1.021164</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0.343094</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -9658,17 +9652,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9676,31 +9670,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="5" t="n">
+        <v>0.173267</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.268051</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0.235681</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>-0.032006</v>
+        <v>1.365513</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>0.005014</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.548615</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.527451</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -9716,47 +9702,41 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F90" s="5" t="n">
+        <v>0.268051</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.235681</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0.168984</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.548615</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0.527451</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0.870545</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -9772,15 +9752,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cash acquired from the Transaction, net of transaction costs</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Common shares issued for the exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -9802,12 +9786,10 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.009271</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1875</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.0055</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -9828,12 +9810,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Proceeds from units issued</t>
+          <t>Cash interest expense paid</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -9857,8 +9839,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n">
-        <v>1.455</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -9884,12 +9868,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Proceeds from options exercised</t>
+          <t>Total shareholders’ equity $ 3,219,148 5,500 17,107 (770,932) 2,470,823 1,000,000 (5,885) 81,110 (617,501)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -9913,18 +9897,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>8e-06</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>2.928547</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -9940,12 +9922,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Issuance costs</t>
+          <t>Deficit $ (8,297,458) - - (770,932) (9,068,390) - - -</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -9969,18 +9951,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-9.685891</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-0.617501</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -9996,12 +9976,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Loans payable advanced</t>
+          <t>Reserves $ 475,088 - 17,107 - 492,195 - - 81,110</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -10025,13 +10005,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0.573305</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -10052,12 +10032,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>$  - -   - -                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         statements.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Repayment of loans payable and convertible debt</t>
+          <t>Common shares # 50,000 - - - - - consolidated 55,760,744 55,810,744</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -10081,18 +10061,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="5" t="n">
-        <v>-0.176456</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>75.810744</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>20</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -10108,15 +10086,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cash interest paid on loans payable and convertible debt</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -10132,18 +10114,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H97" s="5" t="n">
+        <v>-0.123855</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.028029</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.699369</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>-0.770932</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -10164,27 +10142,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Change in cash</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0.173267</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>0.09478399999999999</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>-0.03237</v>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -10192,10 +10172,12 @@
         </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.183102</v>
-      </c>
-      <c r="J98" s="5" t="n">
-        <v>-1.021164</v>
+        <v>0.00565</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -10216,38 +10198,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>0.173267</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>0.268051</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>0.235681</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>1.365513</v>
-      </c>
-      <c r="J99" s="5" t="n">
-        <v>1.548615</v>
+        <v>1.592538</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -10268,17 +10254,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10286,20 +10272,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F100" s="5" t="n">
-        <v>0.268051</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>0.235681</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>0.168984</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I100" s="5" t="n">
-        <v>1.548615</v>
+        <v>-0.032006</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0.527451</v>
+        <v>0.005014</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -10320,17 +10312,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cash income taxes paid</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>IncomeTaxPaidSupplementalData</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10353,10 +10345,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="5" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -10382,19 +10372,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Common shares issued for the exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Cash acquired from the Transaction, net of transaction costs</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -10416,10 +10402,12 @@
         </is>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.009271</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -10440,12 +10428,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Warrants issued as finders fees</t>
+          <t>Proceeds from units issued</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -10470,7 +10458,7 @@
         </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0.009645000000000001</v>
+        <v>1.455</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -10496,12 +10484,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 38,153,574 6,712,012 949 29,870</t>
+          <t>Proceeds from options exercised</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -10526,10 +10514,12 @@
         </is>
       </c>
       <c r="I104" s="5" t="n">
-        <v>1.144742</v>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>-5.598089</v>
+        <v>0.02</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -10550,12 +10540,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Shares issued for the Transaction 5,113,271 1,278,318 - -</t>
+          <t>Issuance costs</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -10580,7 +10570,7 @@
         </is>
       </c>
       <c r="I105" s="5" t="n">
-        <v>1.278318</v>
+        <v>-0.021</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -10606,12 +10596,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Options acquired from the Transaction - - - 82,906</t>
+          <t>Loans payable advanced</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -10636,7 +10626,7 @@
         </is>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.08290599999999999</v>
+        <v>0.01</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -10662,12 +10652,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Units issued in private placement 11,245,200 2,811,300 - -</t>
+          <t>Repayment of loans payable and convertible debt</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -10692,7 +10682,7 @@
         </is>
       </c>
       <c r="I107" s="5" t="n">
-        <v>2.8113</v>
+        <v>-0.176456</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -10718,12 +10708,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Issuance costs in private placement - (21,000) - -</t>
+          <t>Cash interest paid on loans payable and convertible debt</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -10748,7 +10738,7 @@
         </is>
       </c>
       <c r="I108" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.028029</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -10774,15 +10764,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Issuance of agent warrants - (9,645) - 9,645</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Cash income taxes paid</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -10832,12 +10826,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Special warrants exercised 298,699 29,870 - (29,870)</t>
+          <t>Warrants issued as finders fees</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -10861,10 +10855,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="5" t="n">
+        <v>0.009645000000000001</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -10895,7 +10887,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Options exercised 200,000 53,163 - (33,163)</t>
+          <t>Balance, December 31, 2021 38,153,574 6,712,012 949 29,870</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -10920,12 +10912,10 @@
         </is>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.144742</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>-5.598089</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -10951,7 +10941,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Reclassification of the conversion feature - - (949) 949</t>
+          <t>Shares issued for the Transaction 5,113,271 1,278,318 - -</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -10975,10 +10965,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="5" t="n">
+        <v>1.278318</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -11009,7 +10997,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation assets 750,000 187,500 - -</t>
+          <t>Options acquired from the Transaction - - - 82,906</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -11034,7 +11022,7 @@
         </is>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0.1875</v>
+        <v>0.08290599999999999</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -11065,14 +11053,10 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 414,751</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Units issued in private placement 11,245,200 2,811,300 - -</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -11094,7 +11078,7 @@
         </is>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0.414751</v>
+        <v>2.8113</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -11125,14 +11109,10 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Issuance costs in private placement - (21,000) - -</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -11154,10 +11134,12 @@
         </is>
       </c>
       <c r="I115" s="5" t="n">
-        <v>-2.699369</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>-2.699369</v>
+        <v>-0.021</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -11183,7 +11165,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 55,760,744 11,041,518 - 475,088</t>
+          <t>Issuance of agent warrants - (9,645) - 9,645</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -11207,11 +11189,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="5" t="n">
-        <v>3.219148</v>
-      </c>
-      <c r="J116" s="5" t="n">
-        <v>-8.297458000000001</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -11237,7 +11223,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Shares issued for the acquisition of exploration and evaluation assets 50,000 5,500 - -</t>
+          <t>Special warrants exercised 298,699 29,870 - (29,870)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -11261,8 +11247,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="5" t="n">
-        <v>0.0055</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -11293,14 +11281,10 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 17,107</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Options exercised 200,000 53,163 - (33,163)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -11322,7 +11306,7 @@
         </is>
       </c>
       <c r="I118" s="5" t="n">
-        <v>0.017107</v>
+        <v>0.02</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -11353,7 +11337,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 55,810,744 11,047,018 - 492,195</t>
+          <t>Reclassification of the conversion feature - - (949) 949</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -11377,11 +11361,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="5" t="n">
-        <v>2.470823</v>
-      </c>
-      <c r="J119" s="5" t="n">
-        <v>-9.068390000000001</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -11402,33 +11390,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>-0.000234</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>-0.129781</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>-0.03703</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>-0.082964</v>
+          <t>Shares issued for exploration and evaluation assets 750,000 187,500 - -</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I120" s="5" t="n">
-        <v>-0.073265</v>
+        <v>0.1875</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -11454,17 +11446,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Share-based compensation - - - 414,751</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11488,7 +11480,7 @@
         </is>
       </c>
       <c r="I121" s="5" t="n">
-        <v>-0.002225</v>
+        <v>0.414751</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -11514,17 +11506,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Loss for the year - - - -</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11548,12 +11540,10 @@
         </is>
       </c>
       <c r="I122" s="5" t="n">
-        <v>-0.010779</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.699369</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>-2.699369</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -11574,19 +11564,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2022 55,760,744 11,041,518 - 475,088</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -11602,16 +11588,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" s="5" t="n">
-        <v>0.00494</v>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I123" s="5" t="n">
-        <v>-0.007547</v>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.219148</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>-8.297458000000001</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -11632,12 +11618,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Due to related party</t>
+          <t>Shares issued for the acquisition of exploration and evaluation assets 50,000 5,500 - -</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -11662,7 +11648,7 @@
         </is>
       </c>
       <c r="I124" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0055</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -11688,17 +11674,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Share-based compensation - - - 17,107</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11716,11 +11702,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H125" s="5" t="n">
-        <v>-0.078024</v>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I125" s="5" t="n">
-        <v>-0.083316</v>
+        <v>0.017107</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -11746,12 +11734,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Proceeds received from exercise of warrants</t>
+          <t>Balance, December 31, 2023 55,810,744 11,047,018 - 492,195</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -11770,18 +11758,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H126" s="5" t="n">
-        <v>0.011327</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>2.470823</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>-9.068390000000001</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -11802,37 +11788,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>0.200001</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>0.149059</v>
+          <t>Depreciation expense</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H127" s="5" t="n">
-        <v>0.011327</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>0.000975</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -11858,19 +11844,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Net decrease in cash</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -11887,10 +11869,10 @@
         </is>
       </c>
       <c r="H128" s="5" t="n">
-        <v>-0.06669700000000001</v>
+        <v>0.010275</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>-0.083316</v>
+        <v>0.00565</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -11916,15 +11898,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Transfer of fair value of share purchase warrants to share capital from warrant reserve upon exercise</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -11940,13 +11926,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" s="5" t="n">
-        <v>0.005912</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>0.414751</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -11970,10 +11956,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Adjustments for non-cash items</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2021           2020</t>
+          <t>Unrealized foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -11992,15 +11982,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H130" s="5" t="n">
+        <v>-0.002348</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>0.004699</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -12026,19 +12012,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -12049,16 +12031,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G131" s="5" t="n">
-        <v>-0.03703</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>-0.082964</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>1.592538</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -12084,17 +12068,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>GST receivables</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12107,16 +12091,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G132" s="5" t="n">
-        <v>-0.03237</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H132" s="5" t="n">
-        <v>-0.078024</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004084</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>-0.002201</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -12142,19 +12126,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Decrease in cash</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Deferred transaction costs</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -12165,11 +12145,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G133" s="5" t="n">
-        <v>-0.03237</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H133" s="5" t="n">
-        <v>-0.06669700000000001</v>
+        <v>-0.049279</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -12200,17 +12182,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12218,23 +12200,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F134" s="5" t="n">
-        <v>0.044909</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H134" s="5" t="n">
+        <v>0.006348</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>-0.032006</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -12260,39 +12240,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="n">
-        <v>-0.0265</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>0.0265</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H135" s="5" t="n">
+        <v>0.07735300000000001</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>-0.132974</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -12318,17 +12298,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12336,21 +12316,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>0.004097</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>0.00466</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>-0.08559</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>-0.8479370000000001</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -12376,37 +12356,41 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Net cash used by operating activities</t>
+          <t>Purchases of property and equipment</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="n">
-        <v>-0.026734</v>
-      </c>
-      <c r="F137" s="5" t="n">
-        <v>-0.054275</v>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>-0.03237</v>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="5" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -12432,24 +12416,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>0.200001</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>0.2</v>
+          <t>Cash acquired from Transaction, net of costs</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -12461,10 +12445,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I138" s="5" t="n">
+        <v>-0.009271</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -12495,31 +12477,27 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Share subscription payable</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F139" s="5" t="n">
-        <v>-0.050941</v>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H139" s="5" t="n">
+        <v>1.3563</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -12550,12 +12528,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Fair value of agent’s warrants issued</t>
+          <t>Proceeds from issuance of units</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -12564,8 +12542,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n">
-        <v>0.010438</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -12577,10 +12557,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I140" s="5" t="n">
+        <v>1.455</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -12604,33 +12582,37 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Proceeds from loan payable</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>2.9e-05</v>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>0.096452</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -12661,12 +12643,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Repayment of debt</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>RepaymentOfDebt</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12674,8 +12656,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n">
-        <v>0.173267</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -12687,10 +12671,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I142" s="5" t="n">
+        <v>-0.176456</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -12721,19 +12703,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cash, end of period</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="n">
-        <v>0.173267</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>0.268051</v>
+          <t>Payment of interest payable</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -12745,10 +12727,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I143" s="5" t="n">
+        <v>-0.028029</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -12774,12 +12754,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fair value of agent warrants granted</t>
+          <t>Change in cash and restricted cash</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -12788,23 +12768,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F144" s="5" t="n">
-        <v>0.010438</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H144" s="5" t="n">
+        <v>1.218706</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0.183102</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -12825,22 +12803,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Consulting fees 9</t>
+          <t>Cash and restricted cash, beginning of year</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12858,43 +12836,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J145" s="5" t="n">
-        <v>0.095605</v>
-      </c>
-      <c r="K145" s="5" t="n">
-        <v>0.06320199999999999</v>
-      </c>
-      <c r="L145" s="5" t="n">
-        <v>0.07525900000000001</v>
+      <c r="H145" s="5" t="n">
+        <v>0.146807</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>1.365513</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Depreciation expense</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Cash and restricted cash, end of year</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -12910,49 +12894,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>1.365513</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>1.548615</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K146" s="5" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="L146" s="5" t="n">
-        <v>0.0029</v>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>x   Paid $nil for income taxes.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>x   Paid $nil for income taxes. total</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -12968,42 +12948,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H147" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K147" s="5" t="n">
-        <v>0.024522</v>
-      </c>
-      <c r="L147" s="5" t="n">
-        <v>0.031894</v>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>x   Paid $nil for income taxes.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Insurance expense</t>
+          <t>Total shareholders’ equity $ 1,268,597 - (123,855) 1,144,742 1,278,318 82,906 2,811,300 (21,000) - - 20,000 - 187,500 414,751 (2,699,369)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -13022,45 +13002,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H148" s="5" t="n">
+        <v>8e-06</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>0.012024</v>
-      </c>
-      <c r="J148" s="5" t="n">
-        <v>0.037101</v>
-      </c>
-      <c r="K148" s="5" t="n">
-        <v>0.036234</v>
-      </c>
-      <c r="L148" s="5" t="n">
-        <v>0.044598</v>
+        <v>3.219148</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>x   Paid $nil for income taxes.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Investor relations 9</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Deficit $ (5,474,234) - (123,855) (5,598,089) - - - - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -13076,47 +13056,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J149" s="5" t="n">
-        <v>0.143426</v>
-      </c>
-      <c r="K149" s="5" t="n">
-        <v>0.13809</v>
-      </c>
-      <c r="L149" s="5" t="n">
-        <v>0.07239900000000001</v>
+      <c r="H149" s="5" t="n">
+        <v>-8.297458000000001</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>-2.699369</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>x   Paid $nil for income taxes.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Legal and professional fees</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Reserves $ 29,870 - - 29,870 - 82,906 - - 9,645 (29,870) (33,163) 949 - 414,751</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -13132,10 +13110,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>0.475088</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -13147,86 +13123,90 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K150" s="5" t="n">
-        <v>0.087326</v>
-      </c>
-      <c r="L150" s="5" t="n">
-        <v>0.07628</v>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Management fees 9</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J151" s="5" t="n">
-        <v>0.217426</v>
-      </c>
-      <c r="K151" s="5" t="n">
-        <v>0.158314</v>
-      </c>
-      <c r="L151" s="5" t="n">
-        <v>0.18642</v>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>-0.000234</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>-0.129781</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>-0.03703</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>-0.082964</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>-0.073265</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Share-based compensation 8(d),9</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -13247,18 +13227,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I152" s="5" t="n">
+        <v>-0.002225</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K152" s="5" t="n">
-        <v>0.08111</v>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -13269,17 +13249,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Transfer agent and exchange fees</t>
+          <t>Due to related party</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -13304,37 +13284,43 @@
         </is>
       </c>
       <c r="I153" s="5" t="n">
-        <v>0.013612</v>
-      </c>
-      <c r="J153" s="5" t="n">
-        <v>0.020031</v>
-      </c>
-      <c r="K153" s="5" t="n">
-        <v>0.020889</v>
-      </c>
-      <c r="L153" s="5" t="n">
-        <v>0.037888</v>
+        <v>0.0105</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13353,42 +13339,44 @@
         </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>0.120904</v>
+        <v>-0.078024</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>1.103701</v>
-      </c>
-      <c r="J154" s="5" t="n">
-        <v>0.708368</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>0.612587</v>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v>0.5276380000000001</v>
+        <v>-0.083316</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Proceeds received from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -13404,10 +13392,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H155" s="5" t="n">
+        <v>0.011327</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -13419,49 +13405,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K155" s="5" t="n">
-        <v>-0.002445</v>
-      </c>
-      <c r="L155" s="5" t="n">
-        <v>-0.012766</v>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 6(b)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.200001</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.149059</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H156" s="5" t="n">
+        <v>0.011327</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13473,8 +13461,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K156" s="5" t="n">
-        <v>-0.002469</v>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -13485,22 +13475,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Interest income 5</t>
+          <t>Net decrease in cash</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13518,15 +13508,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H157" s="5" t="n">
+        <v>-0.06669700000000001</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>-0.083316</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -13538,24 +13524,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L157" s="5" t="n">
-        <v>0.004312</v>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Other income 6(a)</t>
+          <t>Transfer of fair value of share purchase warrants to share capital from warrant reserve upon exercise</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -13574,10 +13562,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H158" s="5" t="n">
+        <v>0.005912</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13594,31 +13580,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L158" s="5" t="n">
-        <v>0.051188</v>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>2021           2020</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -13649,32 +13629,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K159" s="5" t="n">
-        <v>-0.617501</v>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v>-0.484904</v>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -13687,15 +13671,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G160" s="5" t="n">
+        <v>-0.03703</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>-0.082964</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13707,30 +13687,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K160" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L160" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -13741,44 +13729,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G161" s="5" t="n">
+        <v>-0.03237</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>38.116862</v>
-      </c>
-      <c r="I161" s="5" t="n">
-        <v>49.025411</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>55.796635</v>
-      </c>
-      <c r="K161" s="5" t="n">
-        <v>58.761564</v>
-      </c>
-      <c r="L161" s="5" t="n">
-        <v>77.133793</v>
+        <v>-0.078024</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Depreciation expense 6</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Decrease in cash</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -13789,24 +13787,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I162" s="5" t="n">
-        <v>0.000975</v>
-      </c>
-      <c r="J162" s="5" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>0.0029</v>
+      <c r="G162" s="5" t="n">
+        <v>-0.03237</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>-0.06669700000000001</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -13817,22 +13817,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Legal and professional fees 9</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -13840,10 +13840,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F163" s="5" t="n">
+        <v>0.044909</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -13860,11 +13858,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J163" s="5" t="n">
-        <v>0.114944</v>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>0.087326</v>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -13875,46 +13877,54 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Office expense</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>-0.0265</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>0.0265</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H164" s="5" t="n">
-        <v>0.002727</v>
-      </c>
-      <c r="I164" s="5" t="n">
-        <v>0.022649</v>
-      </c>
-      <c r="J164" s="5" t="n">
-        <v>0.059828</v>
-      </c>
-      <c r="K164" s="5" t="n">
-        <v>0.017068</v>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -13925,34 +13935,34 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Share-based compensation 9,8(d)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F165" s="5" t="n">
+        <v>0.004097</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.00466</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -13964,11 +13974,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J165" s="5" t="n">
-        <v>0.017107</v>
-      </c>
-      <c r="K165" s="5" t="n">
-        <v>0.08111</v>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -13979,34 +13993,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>General expenses</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used by operating activities</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>-0.026734</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>-0.054275</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>-0.03237</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -14023,8 +14035,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K166" s="5" t="n">
-        <v>0.007454</v>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -14035,50 +14049,54 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Proceeds from issuance of common shares</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>0.200001</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H167" s="5" t="n">
-        <v>0.002951</v>
-      </c>
-      <c r="I167" s="5" t="n">
-        <v>0.00313</v>
-      </c>
-      <c r="J167" s="5" t="n">
-        <v>-0.003622</v>
-      </c>
-      <c r="K167" s="5" t="n">
-        <v>-0.002445</v>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -14089,29 +14107,31 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 5(b)</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F168" s="5" t="n">
+        <v>-0.050941</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -14128,11 +14148,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J168" s="5" t="n">
-        <v>-0.058942</v>
-      </c>
-      <c r="K168" s="5" t="n">
-        <v>-0.002469</v>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -14143,50 +14167,52 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Fair value of agent’s warrants issued</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F169" s="5" t="n">
+        <v>0.010438</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H169" s="5" t="n">
-        <v>-0.123855</v>
-      </c>
-      <c r="I169" s="5" t="n">
-        <v>-2.699369</v>
-      </c>
-      <c r="J169" s="5" t="n">
-        <v>-0.770932</v>
-      </c>
-      <c r="K169" s="5" t="n">
-        <v>-0.617501</v>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -14197,50 +14223,46 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>2.9e-05</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I170" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="J170" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K170" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -14251,22 +14273,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Consulting fees 12</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -14274,10 +14296,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F171" s="5" t="n">
+        <v>0.173267</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -14289,11 +14309,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="5" t="n">
-        <v>0.041604</v>
-      </c>
-      <c r="J171" s="5" t="n">
-        <v>0.095605</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -14309,29 +14333,29 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Depreciation expense 7</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>0.173267</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.268051</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -14343,11 +14367,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I172" s="5" t="n">
-        <v>0.000975</v>
-      </c>
-      <c r="J172" s="5" t="n">
-        <v>0.0029</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -14363,33 +14391,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Interest expense 12</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Fair value of agent warrants granted</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F173" s="5" t="n">
+        <v>0.010438</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -14401,8 +14423,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="5" t="n">
-        <v>0.00565</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -14433,7 +14457,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Consulting fees 9</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -14461,21 +14485,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I174" s="5" t="n">
-        <v>0.298823</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J174" s="5" t="n">
-        <v>0.143426</v>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.095605</v>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>0.06320199999999999</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>0.07525900000000001</v>
       </c>
     </row>
     <row r="175">
@@ -14491,14 +14513,10 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Legal and professional fees 12</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Depreciation expense</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -14519,21 +14537,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I175" s="5" t="n">
-        <v>0.197469</v>
-      </c>
-      <c r="J175" s="5" t="n">
-        <v>0.21237</v>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>0.0029</v>
       </c>
     </row>
     <row r="176">
@@ -14549,12 +14567,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Management fees 12</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -14577,21 +14595,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I176" s="5" t="n">
-        <v>0.0775</v>
-      </c>
-      <c r="J176" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>0.024522</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>0.031894</v>
       </c>
     </row>
     <row r="177">
@@ -14607,7 +14625,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Repair and maintenance</t>
+          <t>Insurance expense</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -14632,22 +14650,16 @@
         </is>
       </c>
       <c r="I177" s="5" t="n">
-        <v>0.018644</v>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012024</v>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>0.037101</v>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>0.036234</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>0.044598</v>
       </c>
     </row>
     <row r="178">
@@ -14663,10 +14675,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Share-based compensation 12, 11(d)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Investor relations 9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -14687,21 +14703,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I178" s="5" t="n">
-        <v>0.414751</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J178" s="5" t="n">
-        <v>0.017107</v>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.143426</v>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>0.13809</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>0.07239900000000001</v>
       </c>
     </row>
     <row r="179">
@@ -14712,15 +14726,19 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Listing expense 5</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Legal and professional fees</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -14741,23 +14759,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I179" s="5" t="n">
-        <v>1.592538</v>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K179" s="5" t="n">
+        <v>0.087326</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>0.07628</v>
       </c>
     </row>
     <row r="180">
@@ -14768,15 +14784,19 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 6</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Management fees 9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -14803,17 +14823,13 @@
         </is>
       </c>
       <c r="J180" s="5" t="n">
-        <v>0.058942</v>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.217426</v>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>0.158314</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>0.18642</v>
       </c>
     </row>
     <row r="181">
@@ -14829,14 +14845,10 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation 8(d),9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14852,21 +14864,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H181" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I181" s="5" t="n">
-        <v>0.041604</v>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K181" s="5" t="n">
+        <v>0.08111</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -14887,14 +14901,10 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Interest expense 8, 9, 11</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Transfer agent and exchange fees</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -14910,26 +14920,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H182" s="5" t="n">
-        <v>0.010275</v>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.00565</v>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013612</v>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>0.020031</v>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>0.020889</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>0.037888</v>
       </c>
     </row>
     <row r="183">
@@ -14945,12 +14951,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Legal and professional fees 11</t>
+          <t>Operating expenses total</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -14969,25 +14975,19 @@
         </is>
       </c>
       <c r="H183" s="5" t="n">
-        <v>0.079902</v>
+        <v>0.120904</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>0.197469</v>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.103701</v>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>0.708368</v>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>0.612587</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>0.5276380000000001</v>
       </c>
     </row>
     <row r="184">
@@ -14998,17 +14998,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Management fees 11</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -15026,26 +15026,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="I184" s="5" t="n">
-        <v>0.0775</v>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K184" s="5" t="n">
+        <v>-0.002445</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>-0.012766</v>
       </c>
     </row>
     <row r="185">
@@ -15056,12 +15056,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Share-based compensation 10, 11</t>
+          <t>Impairment of exploration and evaluation assets 6(b)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -15085,18 +15085,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I185" s="5" t="n">
-        <v>0.414751</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K185" s="5" t="n">
+        <v>-0.002469</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -15112,15 +15112,19 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Listing expense 4</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Interest income 5</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -15141,8 +15145,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I186" s="5" t="n">
-        <v>1.592538</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -15154,10 +15160,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L186" s="5" t="n">
+        <v>0.004312</v>
       </c>
     </row>
     <row r="187">
@@ -15168,35 +15172,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Other income 6(a)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F187" s="5" t="n">
-        <v>0.003331</v>
-      </c>
-      <c r="G187" s="5" t="n">
-        <v>0.001477</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>0.0066</v>
-      </c>
-      <c r="I187" s="5" t="n">
-        <v>0.001921</v>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -15208,10 +15216,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L187" s="5" t="n">
+        <v>0.051188</v>
       </c>
     </row>
     <row r="188">
@@ -15222,17 +15228,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Professional fees 5</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -15250,26 +15256,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="5" t="n">
-        <v>0.053133</v>
-      </c>
-      <c r="I188" s="5" t="n">
-        <v>0.059587</v>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K188" s="5" t="n">
+        <v>-0.617501</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>-0.484904</v>
       </c>
     </row>
     <row r="189">
@@ -15280,15 +15286,19 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Rent expense 5</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -15309,23 +15319,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I189" s="5" t="n">
-        <v>0.0005</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K189" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="190">
@@ -15336,50 +15344,44 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F190" s="5" t="n">
-        <v>0.032038</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>0.011488</v>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>0.023231</v>
+        <v>38.116862</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>0.011257</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>49.025411</v>
+      </c>
+      <c r="J190" s="5" t="n">
+        <v>55.796635</v>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>58.761564</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>77.133793</v>
       </c>
     </row>
     <row r="191">
@@ -15390,19 +15392,15 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Depreciation expense 6</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -15418,21 +15416,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H191" s="5" t="n">
-        <v>0.082964</v>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I191" s="5" t="n">
-        <v>0.073265</v>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000975</v>
+      </c>
+      <c r="J191" s="5" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>0.0029</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -15448,17 +15444,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Legal and professional fees 9</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -15466,27 +15462,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F192" s="5" t="n">
-        <v>-0.129781</v>
-      </c>
-      <c r="G192" s="5" t="n">
-        <v>-0.03703</v>
-      </c>
-      <c r="H192" s="5" t="n">
-        <v>-0.082964</v>
-      </c>
-      <c r="I192" s="5" t="n">
-        <v>-0.073265</v>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="n">
+        <v>0.114944</v>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>0.087326</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -15502,15 +15502,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Office expense</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -15527,20 +15531,16 @@
         </is>
       </c>
       <c r="H193" s="5" t="n">
-        <v>5.069561</v>
+        <v>0.002727</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>5.113271</v>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022649</v>
+      </c>
+      <c r="J193" s="5" t="n">
+        <v>0.059828</v>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>0.017068</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -15556,12 +15556,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity $ 226,924 11,327 (82,964) 155,287</t>
+          <t>Share-based compensation 9,8(d)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -15580,21 +15580,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" s="5" t="n">
-        <v>0.082022</v>
-      </c>
-      <c r="I194" s="5" t="n">
-        <v>-0.073265</v>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>0.017107</v>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>0.08111</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -15610,12 +15610,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Deficit $ (167,045) - (82,964) (250,009)</t>
+          <t>General expenses</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -15634,21 +15634,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="5" t="n">
-        <v>-0.323274</v>
-      </c>
-      <c r="I195" s="5" t="n">
-        <v>-0.073265</v>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K195" s="5" t="n">
+        <v>0.007454</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -15664,15 +15666,19 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Warrant reserve $ 10,438 (5,912) - 4,526</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -15689,22 +15695,16 @@
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>0.004526</v>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002951</v>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>0.00313</v>
+      </c>
+      <c r="J196" s="5" t="n">
+        <v>-0.003622</v>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>-0.002445</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>statements.</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>statements.</t>
+          <t>Impairment of exploration and evaluation assets 5(b)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -15754,15 +15754,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J197" s="5" t="n">
+        <v>-0.058942</v>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>-0.002469</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -15778,15 +15774,19 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>are</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -15802,25 +15802,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H198" s="5" t="n">
+        <v>-0.123855</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>-2.699369</v>
+      </c>
+      <c r="J198" s="5" t="n">
+        <v>-0.770932</v>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>-0.617501</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -15834,13 +15826,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2021        2020</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -15856,25 +15856,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H199" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="J199" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -15890,17 +15882,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Consulting fees 12</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -15908,24 +15900,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F200" s="5" t="n">
-        <v>0.049503</v>
-      </c>
-      <c r="G200" s="5" t="n">
-        <v>0.024065</v>
-      </c>
-      <c r="H200" s="5" t="n">
-        <v>0.053133</v>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="n">
+        <v>0.041604</v>
+      </c>
+      <c r="J200" s="5" t="n">
+        <v>0.095605</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -15946,42 +15940,40 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Depreciation expense 7</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F201" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>0.000975</v>
+      </c>
+      <c r="J201" s="5" t="n">
+        <v>0.0029</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -16002,17 +15994,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Interest expense 12</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -16020,19 +16012,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F202" s="5" t="n">
-        <v>4.194522</v>
-      </c>
-      <c r="G202" s="5" t="n">
-        <v>5.000001</v>
-      </c>
-      <c r="H202" s="5" t="n">
-        <v>5.069561</v>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.00565</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -16058,15 +16054,19 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Total 263,954 (37,030) 226,924 11,327</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -16077,21 +16077,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G203" s="5" t="n">
-        <v>0.155287</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>-0.082964</v>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>0.298823</v>
+      </c>
+      <c r="J203" s="5" t="n">
+        <v>0.143426</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -16112,15 +16112,19 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>- total</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>Legal and professional fees 12</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -16141,15 +16145,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I204" s="5" t="n">
+        <v>0.197469</v>
+      </c>
+      <c r="J204" s="5" t="n">
+        <v>0.21237</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -16170,15 +16170,19 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Deficit (130,015) (37,030) (167,045)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>Management fees 12</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -16189,21 +16193,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G205" s="5" t="n">
-        <v>-0.250009</v>
-      </c>
-      <c r="H205" s="5" t="n">
-        <v>-0.082964</v>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="J205" s="5" t="n">
+        <v>0.12</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -16224,12 +16228,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>- these payment reserve 44,909</t>
+          <t>Repair and maintenance</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -16243,16 +16247,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G206" s="5" t="n">
-        <v>0.044909</v>
-      </c>
-      <c r="H206" s="5" t="n">
-        <v>0.044909</v>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>0.018644</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -16278,12 +16284,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>of                                                                                          Share-based                                                                                                                                                                           part</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>of                                                                                          Share-based                                                                                                                                                                           part</t>
+          <t>Share-based compensation 12, 11(d)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -16307,15 +16313,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I207" s="5" t="n">
+        <v>0.414751</v>
+      </c>
+      <c r="J207" s="5" t="n">
+        <v>0.017107</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -16336,12 +16338,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>$                                5</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>- 17,239 integral Amount 338,622</t>
+          <t>Listing expense 5</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -16355,16 +16357,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G208" s="5" t="n">
-        <v>0.355861</v>
-      </c>
-      <c r="H208" s="5" t="n">
-        <v>0.338622</v>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="n">
+        <v>1.592538</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -16390,12 +16394,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>are total</t>
+          <t>Impairment of exploration and evaluation assets 6</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -16424,10 +16428,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J209" s="5" t="n">
+        <v>0.058942</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -16448,15 +16450,19 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>notes                                                        Common                                                                Number shares                               113,270</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>notes                                                        Common                                                                Number shares                               113,270 of 5,000,001</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -16467,16 +16473,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G210" s="5" t="n">
-        <v>5.113271</v>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>5.000001</v>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>0.041604</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -16502,37 +16508,39 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 4 and 5)</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Interest expense 8, 9, 11</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F211" s="5" t="n">
-        <v>0.044909</v>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H211" s="5" t="n">
+        <v>0.010275</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>0.00565</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -16556,15 +16564,25 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" s="5" t="n">
-        <v>2.9e-05</v>
+          <t>Legal and professional fees 11</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16576,15 +16594,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H212" s="5" t="n">
+        <v>0.079902</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>0.197469</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -16610,17 +16624,23 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2018 (date of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>April 30, to April</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" s="5" t="n">
-        <v>3e-05</v>
+          <t>Management fees 11</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16632,15 +16652,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H213" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>0.0775</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -16666,21 +16682,19 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>General and administrative 3,331</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="n">
-        <v>0.000234</v>
+          <t>Share-based compensation 10, 11</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16697,10 +16711,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I214" s="5" t="n">
+        <v>0.414751</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -16726,19 +16738,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Professional fees 49,503</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Listing expense 4</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -16759,10 +16767,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I215" s="5" t="n">
+        <v>1.592538</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -16793,34 +16799,30 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 4) 44,909</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F216" s="5" t="n">
+        <v>0.003331</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>0.001477</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>0.001921</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -16851,12 +16853,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees 32,038</t>
+          <t>Professional fees 5</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -16874,15 +16876,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H217" s="5" t="n">
+        <v>0.053133</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>0.059587</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -16913,12 +16911,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss (129,781)</t>
+          <t>Rent expense 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" s="5" t="n">
-        <v>-0.000234</v>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16935,10 +16935,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I218" s="5" t="n">
+        <v>0.0005</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -16969,34 +16967,30 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted (0.03)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F219" s="5" t="n">
+        <v>0.032038</v>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>0.011488</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>0.023231</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>0.011257</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -17027,16 +17021,18 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 4,194,522</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E220" s="5" t="n">
-        <v>0.351649</v>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17048,15 +17044,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H220" s="5" t="n">
+        <v>0.082964</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>0.073265</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -17087,32 +17079,30 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>$ Total 1 200,000 (234) 199,767 200,000 (50,941) 44,909 (129,781)</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" s="5" t="n">
-        <v>0.263954</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>-0.129781</v>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>-0.03703</v>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>-0.082964</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>-0.073265</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -17138,12 +17128,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -17162,15 +17152,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H222" s="5" t="n">
+        <v>5.069561</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>5.113271</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -17196,49 +17182,1689 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Total shareholders’ equity $ 226,924 11,327 (82,964) 155,287</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>0.082022</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>-0.073265</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Deficit $ (167,045) - (82,964) (250,009)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>-0.323274</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>-0.073265</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Warrant reserve $ 10,438 (5,912) - 4,526</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>0.004526</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>statements.</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>statements.</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2021        2020</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>0.049503</v>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>0.024065</v>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>0.053133</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>4.194522</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>5.000001</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>5.069561</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Total 263,954 (37,030) 226,924 11,327</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>0.155287</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>-0.082964</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>- total</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Deficit (130,015) (37,030) (167,045)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>-0.250009</v>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>-0.082964</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>- these payment reserve 44,909</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="n">
+        <v>0.044909</v>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>0.044909</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>of                                                                                          Share-based                                                                                                                                                                           part</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>of                                                                                          Share-based                                                                                                                                                                           part</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>$                                5</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>- 17,239 integral Amount 338,622</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>0.355861</v>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>0.338622</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>are total</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>notes                                                        Common                                                                Number shares                               113,270</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>notes                                                        Common                                                                Number shares                               113,270 of 5,000,001</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="n">
+        <v>5.113271</v>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>5.000001</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Notes 4 and 5)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>0.044909</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" s="5" t="n">
+        <v>2.9e-05</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2018 (date of</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>April 30, to April</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>General and administrative 3,331</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="n">
+        <v>0.000234</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Professional fees 49,503</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 4) 44,909</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees 32,038</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss (129,781)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" s="5" t="n">
+        <v>-0.000234</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted (0.03)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding 4,194,522</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="n">
+        <v>0.351649</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>$ Total 1 200,000 (234) 199,767 200,000 (50,941) 44,909 (129,781)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" s="5" t="n">
+        <v>0.263954</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
           <t>for             for                                                   (date</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>2018 shares shares grantedINC. CHANGES CANADIAN 29, 2018</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" s="5" t="n">
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" s="5" t="n">
         <v>0.002019</v>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
         <is>
           <t>-</t>
         </is>
